--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N104_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N104_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.87725206006868</v>
+        <v>0.7925534597611605</v>
       </c>
       <c r="D2" t="n">
-        <v>4.263595085212101</v>
+        <v>0.6928342013469664</v>
       </c>
       <c r="E2" t="n">
-        <v>5.395593022219945</v>
+        <v>0.876783866110741</v>
       </c>
       <c r="F2" t="n">
-        <v>5.704196783432804</v>
+        <v>0.9269319773078308</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.73885579963852</v>
+        <v>2.557564067441259</v>
       </c>
       <c r="D3" t="n">
-        <v>16.36789396640892</v>
+        <v>2.65978276954145</v>
       </c>
       <c r="E3" t="n">
-        <v>5.395593022219945</v>
+        <v>0.876783866110741</v>
       </c>
       <c r="F3" t="n">
-        <v>5.704196783432804</v>
+        <v>0.9269319773078308</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.786928150522983</v>
+        <v>0.6153758244599848</v>
       </c>
       <c r="D4" t="n">
-        <v>4.271339203981392</v>
+        <v>0.6940926206469762</v>
       </c>
       <c r="E4" t="n">
-        <v>5.395593022219945</v>
+        <v>0.876783866110741</v>
       </c>
       <c r="F4" t="n">
-        <v>5.704196783432804</v>
+        <v>0.9269319773078308</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
